--- a/servers/maze_main_server_dev/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E274E9C2-8B6A-445E-8805-0B6E2B21FC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A385730-D6F7-40CA-BC5E-6A1147A06EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -722,7 +722,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="2">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2">
         <v>40</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A385730-D6F7-40CA-BC5E-6A1147A06EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DD1989-F288-4388-B974-364312547FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -646,7 +646,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>30020101</v>
+        <v>100201011</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>19</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>30020102</v>
+        <v>100201021</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>30020103</v>
+        <v>100201031</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>21</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DD1989-F288-4388-B974-364312547FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FB9BCA-483F-4821-9867-4C53C4B3B3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -104,14 +104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:3666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:8500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -133,6 +125,90 @@
   </si>
   <si>
     <t>tough_broke_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4667</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6667</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:22300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:17300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:17700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:18000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:13400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:11000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2670</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5400_2:5000_3:5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9600</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -183,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -193,6 +269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -473,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -512,7 +589,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>12</v>
@@ -649,10 +726,10 @@
         <v>100201011</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2">
         <v>40</v>
@@ -663,10 +740,10 @@
         <v>100201021</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D14" s="2">
         <v>40</v>
@@ -677,7 +754,7 @@
         <v>100201031</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" s="2">
         <v>85</v>
@@ -691,7 +768,7 @@
         <v>30030101</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2">
         <v>33</v>
@@ -705,7 +782,7 @@
         <v>30030102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C17" s="2">
         <v>53</v>
@@ -719,7 +796,7 @@
         <v>30030103</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2">
         <v>17</v>
@@ -733,7 +810,7 @@
         <v>30030104</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C19" s="2">
         <v>40</v>
@@ -1215,6 +1292,370 @@
         <v>70</v>
       </c>
       <c r="D53" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>1001011</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="4">
+        <v>0</v>
+      </c>
+      <c r="D54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>1001021</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="4">
+        <v>0</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>1002011</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="4">
+        <v>0</v>
+      </c>
+      <c r="D56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>1002021</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="4">
+        <v>0</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>1004011</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58" s="4">
+        <v>0</v>
+      </c>
+      <c r="D58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>1004021</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="4">
+        <v>0</v>
+      </c>
+      <c r="D59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>3002011</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="4">
+        <v>0</v>
+      </c>
+      <c r="D60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>3002021</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="4">
+        <v>0</v>
+      </c>
+      <c r="D61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>14001011</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="4">
+        <v>0</v>
+      </c>
+      <c r="D62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>14001021</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="4">
+        <v>0</v>
+      </c>
+      <c r="D63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>11101</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" s="4">
+        <v>35</v>
+      </c>
+      <c r="D64" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>11102</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C65" s="4">
+        <v>35</v>
+      </c>
+      <c r="D65" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>11201</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C66" s="4">
+        <v>24</v>
+      </c>
+      <c r="D66" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>11202</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="4">
+        <v>24</v>
+      </c>
+      <c r="D67" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>12101</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" s="4">
+        <v>15</v>
+      </c>
+      <c r="D68" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>12102</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" s="4">
+        <v>24</v>
+      </c>
+      <c r="D69" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>12103</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" s="4">
+        <v>24</v>
+      </c>
+      <c r="D70" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>12201</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="4">
+        <v>24</v>
+      </c>
+      <c r="D71" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>12202</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C72" s="4">
+        <v>24</v>
+      </c>
+      <c r="D72" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>12203</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="4">
+        <v>24</v>
+      </c>
+      <c r="D73" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>13101</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C74" s="4">
+        <v>24</v>
+      </c>
+      <c r="D74" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>13102</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75" s="4">
+        <v>24</v>
+      </c>
+      <c r="D75" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>13103</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C76" s="4">
+        <v>24</v>
+      </c>
+      <c r="D76" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>13201</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C77" s="4">
+        <v>24</v>
+      </c>
+      <c r="D77" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>13202</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" s="4">
+        <v>24</v>
+      </c>
+      <c r="D78" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>13203</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C79" s="4">
+        <v>24</v>
+      </c>
+      <c r="D79" s="4">
         <v>40</v>
       </c>
     </row>
